--- a/artfynd/A 33422-2021 artfynd.xlsx
+++ b/artfynd/A 33422-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1966,6 +1966,109 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114749176</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78446</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vemdalsskalet Klockarfjällsvägen 257 , Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>445465</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6928748</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33422-2021 artfynd.xlsx
+++ b/artfynd/A 33422-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33422-2021 artfynd.xlsx
+++ b/artfynd/A 33422-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89596126</v>
+        <v>89596127</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444929.0050177791</v>
+        <v>444968</v>
       </c>
       <c r="R2" t="n">
-        <v>6928327.074997591</v>
+        <v>6928431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89596129</v>
+        <v>89596126</v>
       </c>
       <c r="B3" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445032.0268228107</v>
+        <v>444929</v>
       </c>
       <c r="R3" t="n">
-        <v>6928535.7939387</v>
+        <v>6928327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +844,14 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89596127</v>
+        <v>89596111</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Parknål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca hispidula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444967.7734563763</v>
+        <v>445205</v>
       </c>
       <c r="R4" t="n">
-        <v>6928430.952647353</v>
+        <v>6928517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,19 +950,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89596128</v>
+        <v>89596112</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445020.0425569176</v>
+        <v>445210</v>
       </c>
       <c r="R5" t="n">
-        <v>6928539.228960108</v>
+        <v>6928517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1051,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,55 +1084,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94995564</v>
+        <v>89596131</v>
       </c>
       <c r="B6" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Strömsfjällvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445086.0189850244</v>
+        <v>445143</v>
       </c>
       <c r="R6" t="n">
-        <v>6928496.057011075</v>
+        <v>6928651</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,27 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tallskog, ås.</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,27 +1169,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>89596109</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445260.1075701897</v>
+        <v>445260</v>
       </c>
       <c r="R7" t="n">
-        <v>6928606.027293501</v>
+        <v>6928606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,19 +1253,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,12 +1289,7 @@
         <v>89596113</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445210.0188669772</v>
+        <v>445210</v>
       </c>
       <c r="R8" t="n">
-        <v>6928517.136842146</v>
+        <v>6928517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,19 +1354,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,15 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89596111</v>
+        <v>94996005</v>
       </c>
       <c r="B9" t="n">
-        <v>73687</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,37 +1403,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>309</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Parknål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca hispidula</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Strömsfjällvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445204.9259637767</v>
+        <v>445262</v>
       </c>
       <c r="R9" t="n">
-        <v>6928517.220654123</v>
+        <v>6928597</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,22 +1458,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mkt gammal sälg, fin skog på åsar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,31 +1483,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89596112</v>
+        <v>94996219</v>
       </c>
       <c r="B10" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,37 +1506,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strömsfjällvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445210.0188669772</v>
+        <v>445370</v>
       </c>
       <c r="R10" t="n">
-        <v>6928517.136842146</v>
+        <v>6928605</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,22 +1561,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På jättesälg ca 45 cm diameter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,31 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94996219</v>
+        <v>89596130</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,38 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Strömsfjällvallen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445370.7671139772</v>
+        <v>445068</v>
       </c>
       <c r="R11" t="n">
-        <v>6928604.672176878</v>
+        <v>6928561</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,27 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På jättesälg ca 45 cm diameter.</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,66 +1683,64 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94996005</v>
+        <v>89596110</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Strömsfjällvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445261.8150698114</v>
+        <v>445258</v>
       </c>
       <c r="R12" t="n">
-        <v>6928597.212872105</v>
+        <v>6928571</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,27 +1764,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mkt gammal sälg, fin skog på åsar.</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,31 +1784,30 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114749176</v>
+        <v>89596128</v>
       </c>
       <c r="B13" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2002,17 +1829,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vemdalsskalet Klockarfjällsvägen 257 , Hjd</t>
+          <t>Strömsfjällvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445465</v>
+        <v>445020</v>
       </c>
       <c r="R13" t="n">
-        <v>6928748</v>
+        <v>6928539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,12 +1865,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,15 +1885,423 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114749176</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vemdalsskalet Klockarfjällsvägen 257 , Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>445465</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6928748</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Bjarne Tutturen</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Bjarne Tutturen</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>89596129</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strömsfjällvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>445032</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6928536</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>89596108</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strömsfjällvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>445213</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6928551</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>94995564</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>445086</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6928497</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tallskog, ås.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
